--- a/data/trans_orig/Predimed_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Predimed_R-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según adherencia a la dieta mediterránea en 2023</t>
+          <t>Población según adherencia a la dieta mediterránea en 2023 (tasa de respuesta: 94,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21430</t>
+          <t>21499</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42151</t>
+          <t>44264</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23904</t>
+          <t>23535</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40513</t>
+          <t>41003</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49641</t>
+          <t>48730</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>78748</t>
+          <t>78267</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,07%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>267760</t>
+          <t>265647</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>288481</t>
+          <t>288412</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>248624</t>
+          <t>248134</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>265233</t>
+          <t>265602</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>520300</t>
+          <t>520781</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>549407</t>
+          <t>550318</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,87%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19736</t>
+          <t>19303</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47266</t>
+          <t>46628</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27657</t>
+          <t>27605</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48076</t>
+          <t>48508</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>52829</t>
+          <t>52191</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>88479</t>
+          <t>86755</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>392918</t>
+          <t>393556</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>420448</t>
+          <t>420881</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>411662</t>
+          <t>411230</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>432081</t>
+          <t>432133</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>811443</t>
+          <t>813167</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>847093</t>
+          <t>847731</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,2%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>68006</t>
+          <t>67022</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>96838</t>
+          <t>97758</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>83279</t>
+          <t>84035</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>110991</t>
+          <t>110674</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>161122</t>
+          <t>160216</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>203510</t>
+          <t>199276</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,28%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>196623</t>
+          <t>195703</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>225455</t>
+          <t>226439</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>77,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>212916</t>
+          <t>213233</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>240628</t>
+          <t>239872</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>65,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>413858</t>
+          <t>418092</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>456246</t>
+          <t>457152</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>74,05%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>74227</t>
+          <t>72260</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>110191</t>
+          <t>108114</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>80477</t>
+          <t>86759</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>207234</t>
+          <t>205641</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>167467</t>
+          <t>169308</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>304274</t>
+          <t>304004</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>47,16%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>132465</t>
+          <t>134542</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>168429</t>
+          <t>170396</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>70,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>194800</t>
+          <t>196393</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>321557</t>
+          <t>315275</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>340416</t>
+          <t>340686</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>477223</t>
+          <t>475382</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>73,74%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29361</t>
+          <t>29676</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48273</t>
+          <t>47898</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>55465</t>
+          <t>55806</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>74713</t>
+          <t>75503</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>90670</t>
+          <t>90468</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>116788</t>
+          <t>116221</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,82%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>125309</t>
+          <t>125684</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>144221</t>
+          <t>143906</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>128859</t>
+          <t>128069</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>148107</t>
+          <t>147766</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,3%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>260366</t>
+          <t>260933</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>286484</t>
+          <t>286686</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>76,01%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30835</t>
+          <t>30081</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50606</t>
+          <t>51236</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17613</t>
+          <t>17105</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31380</t>
+          <t>30463</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>52966</t>
+          <t>51403</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>79936</t>
+          <t>77385</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>14,83%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>216438</t>
+          <t>215808</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>236209</t>
+          <t>236963</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>223238</t>
+          <t>224155</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>237005</t>
+          <t>237513</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>441727</t>
+          <t>444278</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>468697</t>
+          <t>470260</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>90,15%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>155381</t>
+          <t>156839</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>207797</t>
+          <t>205162</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>74005</t>
+          <t>83789</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>252916</t>
+          <t>254340</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>242384</t>
+          <t>224453</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>438554</t>
+          <t>440893</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,32%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>377500</t>
+          <t>380135</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>429916</t>
+          <t>428458</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>569291</t>
+          <t>567867</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>748202</t>
+          <t>738418</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>968950</t>
+          <t>966611</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1165120</t>
+          <t>1183051</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>84,05%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9317</t>
+          <t>9589</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>39531</t>
+          <t>39925</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>32475</t>
+          <t>33071</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>63759</t>
+          <t>63370</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>39615</t>
+          <t>41595</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>91972</t>
+          <t>92141</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>874695</t>
+          <t>874301</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>904909</t>
+          <t>904637</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>642755</t>
+          <t>643144</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>674039</t>
+          <t>673443</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1528768</t>
+          <t>1528599</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1581125</t>
+          <t>1579145</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,43%</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>390986</t>
+          <t>396623</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>577176</t>
+          <t>579041</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>515200</t>
+          <t>515132</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>727904</t>
+          <t>721511</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>990921</t>
+          <t>986434</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1266726</t>
+          <t>1258894</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,82%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2649186</t>
+          <t>2647321</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2835376</t>
+          <t>2829739</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2733822</t>
+          <t>2740215</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2946526</t>
+          <t>2946594</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>79,16%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5421362</t>
+          <t>5429194</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5697167</t>
+          <t>5701654</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,25%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Predimed_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Predimed_R-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>30602</t>
+          <t>33331</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21499</t>
+          <t>23931</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44264</t>
+          <t>44817</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>31309</t>
+          <t>31671</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23535</t>
+          <t>24487</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41003</t>
+          <t>41075</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>61911</t>
+          <t>65002</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48730</t>
+          <t>52253</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>78267</t>
+          <t>79013</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,48%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>279309</t>
+          <t>284277</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>265647</t>
+          <t>272791</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>288412</t>
+          <t>293677</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>257828</t>
+          <t>283910</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>248134</t>
+          <t>274506</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>265602</t>
+          <t>291094</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>537137</t>
+          <t>568187</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>520781</t>
+          <t>554176</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>550318</t>
+          <t>580936</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,75%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>309911</t>
+          <t>317608</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>309911</t>
+          <t>317608</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>309911</t>
+          <t>317608</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289137</t>
+          <t>315581</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289137</t>
+          <t>315581</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289137</t>
+          <t>315581</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>599048</t>
+          <t>633189</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>599048</t>
+          <t>633189</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>599048</t>
+          <t>633189</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30025</t>
+          <t>30508</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19303</t>
+          <t>21097</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46628</t>
+          <t>47139</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>37163</t>
+          <t>37716</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27605</t>
+          <t>28887</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48508</t>
+          <t>50217</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>67188</t>
+          <t>68224</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>52191</t>
+          <t>52880</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>86755</t>
+          <t>86056</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,12%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>410159</t>
+          <t>424163</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>393556</t>
+          <t>407532</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>420881</t>
+          <t>433574</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>422575</t>
+          <t>451044</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>411230</t>
+          <t>438543</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>432133</t>
+          <t>459873</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>832734</t>
+          <t>875206</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>813167</t>
+          <t>857374</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>847731</t>
+          <t>890550</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,39%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>440184</t>
+          <t>454671</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>440184</t>
+          <t>454671</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>440184</t>
+          <t>454671</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>459738</t>
+          <t>488760</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>459738</t>
+          <t>488760</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>459738</t>
+          <t>488760</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>899922</t>
+          <t>943430</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>899922</t>
+          <t>943430</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>899922</t>
+          <t>943430</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>82657</t>
+          <t>81650</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>67022</t>
+          <t>68545</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>97758</t>
+          <t>96868</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>97311</t>
+          <t>98358</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>84035</t>
+          <t>85242</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>110674</t>
+          <t>112430</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>179968</t>
+          <t>180008</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>160216</t>
+          <t>161333</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>199276</t>
+          <t>202647</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,46%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>210804</t>
+          <t>212428</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>195703</t>
+          <t>197210</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>226439</t>
+          <t>225533</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>67,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>226596</t>
+          <t>231827</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>213233</t>
+          <t>217755</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>239872</t>
+          <t>244943</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>437400</t>
+          <t>444255</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>418092</t>
+          <t>421616</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>457152</t>
+          <t>462930</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>67,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>74,16%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>293461</t>
+          <t>294078</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>293461</t>
+          <t>294078</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>293461</t>
+          <t>294078</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>323907</t>
+          <t>330185</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>323907</t>
+          <t>330185</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>323907</t>
+          <t>330185</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>617368</t>
+          <t>624263</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>617368</t>
+          <t>624263</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>617368</t>
+          <t>624263</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>90493</t>
+          <t>116107</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72260</t>
+          <t>95920</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>108114</t>
+          <t>138089</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>152628</t>
+          <t>133550</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>86759</t>
+          <t>116156</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>205641</t>
+          <t>150571</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>243121</t>
+          <t>249658</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>169308</t>
+          <t>224034</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>304004</t>
+          <t>276741</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>44,39%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>152163</t>
+          <t>170446</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>134542</t>
+          <t>148464</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>170396</t>
+          <t>190633</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>51,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>249406</t>
+          <t>203350</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>196393</t>
+          <t>186329</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>315275</t>
+          <t>220744</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>65,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>401569</t>
+          <t>373795</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>340686</t>
+          <t>346712</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>475382</t>
+          <t>399419</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>55,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>64,07%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>242656</t>
+          <t>286553</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>242656</t>
+          <t>286553</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>242656</t>
+          <t>286553</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>402034</t>
+          <t>336900</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>402034</t>
+          <t>336900</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>402034</t>
+          <t>336900</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>644690</t>
+          <t>623453</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>644690</t>
+          <t>623453</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>644690</t>
+          <t>623453</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>37978</t>
+          <t>40797</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29676</t>
+          <t>31970</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47898</t>
+          <t>52250</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>64691</t>
+          <t>69879</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>55806</t>
+          <t>59565</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>75503</t>
+          <t>81342</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>102668</t>
+          <t>110676</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>90468</t>
+          <t>96921</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>116221</t>
+          <t>124926</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>29,51%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>135604</t>
+          <t>159450</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>125684</t>
+          <t>147997</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>143906</t>
+          <t>168277</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>138881</t>
+          <t>153215</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>128069</t>
+          <t>141752</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>147766</t>
+          <t>163529</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>63,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>274486</t>
+          <t>312664</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>260933</t>
+          <t>298414</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>286686</t>
+          <t>326419</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>77,11%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>173582</t>
+          <t>200247</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>173582</t>
+          <t>200247</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>173582</t>
+          <t>200247</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>203572</t>
+          <t>223094</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>203572</t>
+          <t>223094</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>203572</t>
+          <t>223094</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>377154</t>
+          <t>423340</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>377154</t>
+          <t>423340</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>377154</t>
+          <t>423340</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>40026</t>
+          <t>39897</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30081</t>
+          <t>30517</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>51236</t>
+          <t>51209</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>23746</t>
+          <t>24979</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17105</t>
+          <t>18876</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30463</t>
+          <t>33563</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>63772</t>
+          <t>64876</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>51403</t>
+          <t>53298</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>77385</t>
+          <t>77611</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>227018</t>
+          <t>228299</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>215808</t>
+          <t>216987</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>236963</t>
+          <t>237679</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>230872</t>
+          <t>236266</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>224155</t>
+          <t>227682</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>237513</t>
+          <t>242369</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>457891</t>
+          <t>464565</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>444278</t>
+          <t>451830</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>470260</t>
+          <t>476143</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>89,93%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>267044</t>
+          <t>268196</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>267044</t>
+          <t>268196</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>267044</t>
+          <t>268196</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>254618</t>
+          <t>261245</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>254618</t>
+          <t>261245</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>254618</t>
+          <t>261245</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>521663</t>
+          <t>529441</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>521663</t>
+          <t>529441</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>521663</t>
+          <t>529441</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>180631</t>
+          <t>208492</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>156839</t>
+          <t>182658</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>205162</t>
+          <t>235993</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>184555</t>
+          <t>223874</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>83789</t>
+          <t>202444</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>254340</t>
+          <t>250718</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>365185</t>
+          <t>432366</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>224453</t>
+          <t>398111</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>440893</t>
+          <t>473147</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>33,54%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>404666</t>
+          <t>465340</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>380135</t>
+          <t>437839</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>428458</t>
+          <t>491174</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>637652</t>
+          <t>513142</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>567867</t>
+          <t>486298</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>738418</t>
+          <t>534572</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>69,62%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>65,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1042319</t>
+          <t>978481</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>966611</t>
+          <t>937700</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1183051</t>
+          <t>1012736</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>71,78%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>585297</t>
+          <t>673832</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>585297</t>
+          <t>673832</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>585297</t>
+          <t>673832</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>822207</t>
+          <t>737016</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>822207</t>
+          <t>737016</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>822207</t>
+          <t>737016</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1407504</t>
+          <t>1410847</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1407504</t>
+          <t>1410847</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1407504</t>
+          <t>1410847</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>24107</t>
+          <t>26693</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9589</t>
+          <t>17941</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>39925</t>
+          <t>40745</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>43915</t>
+          <t>44160</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>33071</t>
+          <t>32991</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>63370</t>
+          <t>57601</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>68022</t>
+          <t>70853</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>41595</t>
+          <t>56632</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>92141</t>
+          <t>90712</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>890119</t>
+          <t>755414</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>874301</t>
+          <t>741362</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>904637</t>
+          <t>764166</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>662599</t>
+          <t>774615</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>643144</t>
+          <t>761174</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>673443</t>
+          <t>785784</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1552718</t>
+          <t>1530028</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1528599</t>
+          <t>1510169</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1579145</t>
+          <t>1544249</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>914226</t>
+          <t>782107</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>914226</t>
+          <t>782107</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>914226</t>
+          <t>782107</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>706514</t>
+          <t>818775</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>706514</t>
+          <t>818775</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>706514</t>
+          <t>818775</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1620740</t>
+          <t>1600881</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1620740</t>
+          <t>1600881</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1620740</t>
+          <t>1600881</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3469,32 +3469,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>516519</t>
+          <t>577475</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>396623</t>
+          <t>533687</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>579041</t>
+          <t>631365</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,32 +3504,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>635318</t>
+          <t>664187</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>515132</t>
+          <t>625674</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>721511</t>
+          <t>707948</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1151836</t>
+          <t>1241662</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>986434</t>
+          <t>1175345</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1258894</t>
+          <t>1310511</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>19,3%</t>
         </is>
       </c>
     </row>
@@ -3582,32 +3582,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2709843</t>
+          <t>2699816</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2647321</t>
+          <t>2645926</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2829739</t>
+          <t>2743604</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,32 +3617,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2826408</t>
+          <t>2847367</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2740215</t>
+          <t>2803606</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2946594</t>
+          <t>2885880</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>5536252</t>
+          <t>5547183</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5429194</t>
+          <t>5478334</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5701654</t>
+          <t>5613500</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>82,69%</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3695,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3226362</t>
+          <t>3277291</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3226362</t>
+          <t>3277291</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3226362</t>
+          <t>3277291</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3461726</t>
+          <t>3511554</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3461726</t>
+          <t>3511554</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3461726</t>
+          <t>3511554</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>6688088</t>
+          <t>6788845</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6688088</t>
+          <t>6788845</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6688088</t>
+          <t>6788845</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
